--- a/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:30:57+00:00</t>
+    <t>2026-09-14T12:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:16:24+00:00</t>
+    <t>2026-09-14T12:40:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:40:07+00:00</t>
+    <t>2026-09-14T13:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-sas-pdm-appointment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:01:31+00:00</t>
+    <t>2026-09-22T14:05:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
